--- a/data/hex_xlsx/KESKOB.HE.xlsx
+++ b/data/hex_xlsx/KESKOB.HE.xlsx
@@ -15692,8 +15692,12 @@
       <c r="U103" s="21">
         <v>2409.85</v>
       </c>
-      <c r="V103" s="15"/>
-      <c r="W103" s="15"/>
+      <c r="V103" s="21">
+        <v>2196.49</v>
+      </c>
+      <c r="W103" s="21">
+        <v>2010.04</v>
+      </c>
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
